--- a/raw_images_dataset.xlsx
+++ b/raw_images_dataset.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="193">
   <si>
     <t>图片地址</t>
   </si>
@@ -555,6 +555,60 @@
   </si>
   <si>
     <t>D:\lantek\project-python\p2r-yolo-train\raw_images\B2603030-004.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\a.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\b.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\c.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\d.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\e.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\f.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\g.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\h.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\i.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\j.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\k.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\l.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\m.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\p.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\q.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\r.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\s.png</t>
+  </si>
+  <si>
+    <t>D:\lantek\project-python\p2r-yolo-train\raw_images\w.png</t>
   </si>
 </sst>
 </file>
@@ -567,7 +621,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,13 +642,6 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1050,28 +1097,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1080,118 +1130,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1545,7 +1592,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O157"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="75.9090909090909" customWidth="1"/>
@@ -7218,6 +7265,654 @@
         <v>25</v>
       </c>
     </row>
+    <row r="158" spans="1:15">
+      <c r="A158" t="s">
+        <v>175</v>
+      </c>
+      <c r="B158" s="2" t="str">
+        <f>LEFT(TRIM(RIGHT(SUBSTITUTE(A158,"\",REPT(" ",100)),100)),FIND(".",TRIM(RIGHT(SUBSTITUTE(A158,"\",REPT(" ",100)),100)))-1)</f>
+        <v>a</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158" t="s">
+        <v>16</v>
+      </c>
+      <c r="E158">
+        <v>16</v>
+      </c>
+      <c r="J158" t="s">
+        <v>17</v>
+      </c>
+      <c r="K158" t="s">
+        <v>18</v>
+      </c>
+      <c r="L158" t="s">
+        <v>19</v>
+      </c>
+      <c r="M158" t="s">
+        <v>19</v>
+      </c>
+      <c r="N158">
+        <v>80</v>
+      </c>
+      <c r="O158">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
+      <c r="A159" t="s">
+        <v>176</v>
+      </c>
+      <c r="B159" s="2" t="str">
+        <f>LEFT(TRIM(RIGHT(SUBSTITUTE(A159,"\",REPT(" ",100)),100)),FIND(".",TRIM(RIGHT(SUBSTITUTE(A159,"\",REPT(" ",100)),100)))-1)</f>
+        <v>b</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159" t="s">
+        <v>16</v>
+      </c>
+      <c r="E159">
+        <v>16</v>
+      </c>
+      <c r="J159" t="s">
+        <v>17</v>
+      </c>
+      <c r="K159" t="s">
+        <v>18</v>
+      </c>
+      <c r="L159" t="s">
+        <v>19</v>
+      </c>
+      <c r="M159" t="s">
+        <v>19</v>
+      </c>
+      <c r="N159">
+        <v>80</v>
+      </c>
+      <c r="O159">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
+      <c r="A160" t="s">
+        <v>177</v>
+      </c>
+      <c r="B160" s="2" t="str">
+        <f t="shared" ref="B160:B175" si="5">LEFT(TRIM(RIGHT(SUBSTITUTE(A160,"\",REPT(" ",100)),100)),FIND(".",TRIM(RIGHT(SUBSTITUTE(A160,"\",REPT(" ",100)),100)))-1)</f>
+        <v>c</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160">
+        <v>16</v>
+      </c>
+      <c r="J160" t="s">
+        <v>17</v>
+      </c>
+      <c r="K160" t="s">
+        <v>18</v>
+      </c>
+      <c r="L160" t="s">
+        <v>19</v>
+      </c>
+      <c r="M160" t="s">
+        <v>19</v>
+      </c>
+      <c r="N160">
+        <v>80</v>
+      </c>
+      <c r="O160">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
+      <c r="A161" t="s">
+        <v>178</v>
+      </c>
+      <c r="B161" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>d</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161" t="s">
+        <v>16</v>
+      </c>
+      <c r="E161">
+        <v>16</v>
+      </c>
+      <c r="J161" t="s">
+        <v>17</v>
+      </c>
+      <c r="K161" t="s">
+        <v>18</v>
+      </c>
+      <c r="L161" t="s">
+        <v>19</v>
+      </c>
+      <c r="M161" t="s">
+        <v>19</v>
+      </c>
+      <c r="N161">
+        <v>80</v>
+      </c>
+      <c r="O161">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
+      <c r="A162" t="s">
+        <v>179</v>
+      </c>
+      <c r="B162" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>e</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162">
+        <v>16</v>
+      </c>
+      <c r="J162" t="s">
+        <v>17</v>
+      </c>
+      <c r="K162" t="s">
+        <v>18</v>
+      </c>
+      <c r="L162" t="s">
+        <v>19</v>
+      </c>
+      <c r="M162" t="s">
+        <v>19</v>
+      </c>
+      <c r="N162">
+        <v>80</v>
+      </c>
+      <c r="O162">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
+      <c r="A163" t="s">
+        <v>180</v>
+      </c>
+      <c r="B163" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>f</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163" t="s">
+        <v>16</v>
+      </c>
+      <c r="E163">
+        <v>16</v>
+      </c>
+      <c r="J163" t="s">
+        <v>17</v>
+      </c>
+      <c r="K163" t="s">
+        <v>18</v>
+      </c>
+      <c r="L163" t="s">
+        <v>19</v>
+      </c>
+      <c r="M163" t="s">
+        <v>19</v>
+      </c>
+      <c r="N163">
+        <v>80</v>
+      </c>
+      <c r="O163">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
+      <c r="A164" t="s">
+        <v>181</v>
+      </c>
+      <c r="B164" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>g</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164">
+        <v>16</v>
+      </c>
+      <c r="J164" t="s">
+        <v>17</v>
+      </c>
+      <c r="K164" t="s">
+        <v>18</v>
+      </c>
+      <c r="L164" t="s">
+        <v>19</v>
+      </c>
+      <c r="M164" t="s">
+        <v>19</v>
+      </c>
+      <c r="N164">
+        <v>80</v>
+      </c>
+      <c r="O164">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
+      <c r="A165" t="s">
+        <v>182</v>
+      </c>
+      <c r="B165" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>h</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165" t="s">
+        <v>16</v>
+      </c>
+      <c r="E165">
+        <v>16</v>
+      </c>
+      <c r="J165" t="s">
+        <v>17</v>
+      </c>
+      <c r="K165" t="s">
+        <v>18</v>
+      </c>
+      <c r="L165" t="s">
+        <v>19</v>
+      </c>
+      <c r="M165" t="s">
+        <v>19</v>
+      </c>
+      <c r="N165">
+        <v>80</v>
+      </c>
+      <c r="O165">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
+      <c r="A166" t="s">
+        <v>183</v>
+      </c>
+      <c r="B166" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>i</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166">
+        <v>16</v>
+      </c>
+      <c r="J166" t="s">
+        <v>17</v>
+      </c>
+      <c r="K166" t="s">
+        <v>18</v>
+      </c>
+      <c r="L166" t="s">
+        <v>19</v>
+      </c>
+      <c r="M166" t="s">
+        <v>19</v>
+      </c>
+      <c r="N166">
+        <v>80</v>
+      </c>
+      <c r="O166">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15">
+      <c r="A167" t="s">
+        <v>184</v>
+      </c>
+      <c r="B167" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>j</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167" t="s">
+        <v>16</v>
+      </c>
+      <c r="E167">
+        <v>16</v>
+      </c>
+      <c r="J167" t="s">
+        <v>17</v>
+      </c>
+      <c r="K167" t="s">
+        <v>18</v>
+      </c>
+      <c r="L167" t="s">
+        <v>19</v>
+      </c>
+      <c r="M167" t="s">
+        <v>19</v>
+      </c>
+      <c r="N167">
+        <v>80</v>
+      </c>
+      <c r="O167">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15">
+      <c r="A168" t="s">
+        <v>185</v>
+      </c>
+      <c r="B168" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>k</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="D168" t="s">
+        <v>16</v>
+      </c>
+      <c r="E168">
+        <v>16</v>
+      </c>
+      <c r="J168" t="s">
+        <v>17</v>
+      </c>
+      <c r="K168" t="s">
+        <v>18</v>
+      </c>
+      <c r="L168" t="s">
+        <v>19</v>
+      </c>
+      <c r="M168" t="s">
+        <v>19</v>
+      </c>
+      <c r="N168">
+        <v>80</v>
+      </c>
+      <c r="O168">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15">
+      <c r="A169" t="s">
+        <v>186</v>
+      </c>
+      <c r="B169" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>l</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169" t="s">
+        <v>16</v>
+      </c>
+      <c r="E169">
+        <v>16</v>
+      </c>
+      <c r="J169" t="s">
+        <v>17</v>
+      </c>
+      <c r="K169" t="s">
+        <v>18</v>
+      </c>
+      <c r="L169" t="s">
+        <v>19</v>
+      </c>
+      <c r="M169" t="s">
+        <v>19</v>
+      </c>
+      <c r="N169">
+        <v>80</v>
+      </c>
+      <c r="O169">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15">
+      <c r="A170" t="s">
+        <v>187</v>
+      </c>
+      <c r="B170" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>m</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170">
+        <v>16</v>
+      </c>
+      <c r="J170" t="s">
+        <v>17</v>
+      </c>
+      <c r="K170" t="s">
+        <v>18</v>
+      </c>
+      <c r="L170" t="s">
+        <v>19</v>
+      </c>
+      <c r="M170" t="s">
+        <v>19</v>
+      </c>
+      <c r="N170">
+        <v>80</v>
+      </c>
+      <c r="O170">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15">
+      <c r="A171" t="s">
+        <v>188</v>
+      </c>
+      <c r="B171" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>p</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171">
+        <v>16</v>
+      </c>
+      <c r="J171" t="s">
+        <v>17</v>
+      </c>
+      <c r="K171" t="s">
+        <v>18</v>
+      </c>
+      <c r="L171" t="s">
+        <v>19</v>
+      </c>
+      <c r="M171" t="s">
+        <v>19</v>
+      </c>
+      <c r="N171">
+        <v>80</v>
+      </c>
+      <c r="O171">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
+      <c r="A172" t="s">
+        <v>189</v>
+      </c>
+      <c r="B172" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>q</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172">
+        <v>16</v>
+      </c>
+      <c r="J172" t="s">
+        <v>17</v>
+      </c>
+      <c r="K172" t="s">
+        <v>18</v>
+      </c>
+      <c r="L172" t="s">
+        <v>19</v>
+      </c>
+      <c r="M172" t="s">
+        <v>19</v>
+      </c>
+      <c r="N172">
+        <v>80</v>
+      </c>
+      <c r="O172">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
+      <c r="A173" t="s">
+        <v>190</v>
+      </c>
+      <c r="B173" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>r</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173" t="s">
+        <v>16</v>
+      </c>
+      <c r="E173">
+        <v>16</v>
+      </c>
+      <c r="J173" t="s">
+        <v>17</v>
+      </c>
+      <c r="K173" t="s">
+        <v>18</v>
+      </c>
+      <c r="L173" t="s">
+        <v>19</v>
+      </c>
+      <c r="M173" t="s">
+        <v>19</v>
+      </c>
+      <c r="N173">
+        <v>80</v>
+      </c>
+      <c r="O173">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
+      <c r="A174" t="s">
+        <v>191</v>
+      </c>
+      <c r="B174" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>s</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+      <c r="D174" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174">
+        <v>16</v>
+      </c>
+      <c r="J174" t="s">
+        <v>17</v>
+      </c>
+      <c r="K174" t="s">
+        <v>18</v>
+      </c>
+      <c r="L174" t="s">
+        <v>19</v>
+      </c>
+      <c r="M174" t="s">
+        <v>19</v>
+      </c>
+      <c r="N174">
+        <v>80</v>
+      </c>
+      <c r="O174">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
+      <c r="A175" t="s">
+        <v>192</v>
+      </c>
+      <c r="B175" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>w</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175" t="s">
+        <v>16</v>
+      </c>
+      <c r="E175">
+        <v>16</v>
+      </c>
+      <c r="J175" t="s">
+        <v>17</v>
+      </c>
+      <c r="K175" t="s">
+        <v>18</v>
+      </c>
+      <c r="L175" t="s">
+        <v>19</v>
+      </c>
+      <c r="M175" t="s">
+        <v>19</v>
+      </c>
+      <c r="N175">
+        <v>80</v>
+      </c>
+      <c r="O175">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O157" etc:filterBottomFollowUsedRange="0">
     <extLst/>
